--- a/ig/mc-add-profils-dp/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2778" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASPractitionerRoleProfile</t>
+    <t>AsPractitionerRoleProfile</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de la ressource PractitionerRole dans le contexte de l'Annuaire Santé pour décrire l'exercice professionel et la situation d'exercice | contient les informations décrivant notamment la profession exercée, l'identité d'exercice d'un professionnel, le cadre de son exercice (civil, militaire, etc.) ainsi que les caractéristiques de l'exercice d’un professionnel pendant une période déterminée et dans une structure déterminée.</t>
+    <t>Profil créé à partir de FrPractitionerRoleExercice dans le contexte de l'Annuaire Santé pour décrire l'exercice professionel et la situation d'exercice | contient les informations décrivant notamment la profession exercée, l'identité d'exercice d'un professionnel, le cadre de son exercice (civil, militaire, etc.) ainsi que les caractéristiques de l'exercice d’un professionnel pendant une période déterminée et dans une structure déterminée.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -455,7 +455,7 @@
 </t>
   </si>
   <si>
-    <t>civiliteExercie + nomExercice + prenomExercice (ExerciceProfessionnel)</t>
+    <t>La civilité, le nom et le prénom sous lequels exerce le professionnel.</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour définir l'identité d’exercice d’un professionnel.</t>
@@ -474,13 +474,13 @@
 </t>
   </si>
   <si>
-    <t>Autorité d'enregistrement représentant une institution (Ordre/ARS).</t>
+    <t>Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true".</t>
   </si>
   <si>
-    <t>Synonyme : AutoriteEnregistrement, Ordre</t>
+    <t>Synonymes : InscriptionOrdre</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-education-level</t>
@@ -493,13 +493,10 @@
 </t>
   </si>
   <si>
-    <t>Savoir-faire (qualifications/autres attributions).</t>
+    <t>niveauFormation</t>
   </si>
   <si>
     <t>Le niveau de formation.</t>
-  </si>
-  <si>
-    <t>Synonyme MOS : SavoirFaire</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-smartcard</t>
@@ -512,13 +509,106 @@
 </t>
   </si>
   <si>
-    <t>Numéro de carte du professionnel.</t>
-  </si>
-  <si>
     <t>Données descriptives du moyen d’identification des personnes physiques via une carte de professionnel.</t>
   </si>
   <si>
-    <t>Synonyme MOS : CarteProfessionnel</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les informations de la carte CPx utilisée comme moyen d’identification des personnes physiques.</t>
+  </si>
+  <si>
+    <t>Synonyme : CarteProfessionnel 
+ La carte est rattachée à l’exercice d’une profession donnée et non au professionnel lui-même, un professionnel exerçant simultanément deux professions a deux cartes</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-digital-certificate</t>
+  </si>
+  <si>
+    <t>as-ext-digital-certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
+</t>
+  </si>
+  <si>
+    <t>AS Digital Certificate Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les certificats utilisés par les professionnels et les structures comme moyen d'identification.</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-practitionerrole-end-cause</t>
+  </si>
+  <si>
+    <t>as-ext-practitionerrole-end-cause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-end-cause}
+</t>
+  </si>
+  <si>
+    <t>Motif de fin d'activité, par exemple: décès, retraite libérale, changement de profession, etc.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le motif de fin d'activité du professionnel (décès, retraite libérale, changement de profession par exemple.</t>
+  </si>
+  <si>
+    <t>Synonyme : motifFinActivite</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-practitionerrole-contracted</t>
+  </si>
+  <si>
+    <t>as-ext-practitionerrole-contracted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted}
+</t>
+  </si>
+  <si>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+  </si>
+  <si>
+    <t>Synonyme : secteurConventionnement</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-practitionerrole-hascas</t>
+  </si>
+  <si>
+    <t>as-ext-practitionerrole-hascas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas}
+</t>
+  </si>
+  <si>
+    <t>OPTAM est un dispositif proposé par l’Assurance Maladie aux médecins conventionnés, ayant pour objectif principal de faciliter l’accès aux soins.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le contrat d'accès aux soins (CAS), remplacée récemment par l'option pratique tarifaire maîtrisée (OPTAM).</t>
+  </si>
+  <si>
+    <t>Synonyme : optionContratAccesSoins, optionPratiqueTarifaireMaîtrisée</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-practitionerrole-vitale-accepted</t>
+  </si>
+  <si>
+    <t>as-ext-practitionerrole-vitale-accepted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted}
+</t>
+  </si>
+  <si>
+    <t>L’indicateur Carte Vitale acceptée précisant si le professionnel, dans le cadre de cette situation opérationnelle, dispose des moyens techniques pour prendre en charge la carte vitale ou pas.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire l’indicateur Carte Vitale acceptée (oui/non).</t>
+  </si>
+  <si>
+    <t>Synonyme : carteVitaleAcceptee, optionPratiqueTarifaireMaîtrisée</t>
   </si>
   <si>
     <t>PractitionerRole.modifierExtension</t>
@@ -550,7 +640,7 @@
     <t>Business Identifiers that are specific to a role/location.</t>
   </si>
   <si>
-    <t>Synonyme MOS : idFonctionnel</t>
+    <t>Synonyme : idFonctionnel</t>
   </si>
   <si>
     <t>Often, specific identities are assigned for the agent.</t>
@@ -733,7 +823,7 @@
 </t>
   </si>
   <si>
-    <t>La sitation d'exercice est-elle active? (active | inactive)</t>
+    <t>La situation d'exercice est-elle active? (active | inactive)</t>
   </si>
   <si>
     <t>Whether this practitioner role record is in active use.</t>
@@ -779,7 +869,7 @@
     <t>The start of the period. The boundary is inclusive.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateDebutActivite</t>
+    <t>Synonyme : dateDebutActivite</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -1888,12 +1978,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ84"/>
+  <dimension ref="A1:AJ89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.15625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.33984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="36.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1901,7 +1991,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.7265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2972,7 +3062,7 @@
         <v>72</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
@@ -3180,7 +3270,7 @@
         <v>72</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
@@ -3200,9 +3290,7 @@
       <c r="M13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>71</v>
@@ -3268,13 +3356,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>71</v>
@@ -3284,7 +3372,7 @@
         <v>72</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3296,16 +3384,16 @@
         <v>71</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3372,14 +3460,16 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3389,29 +3479,25 @@
         <v>73</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>71</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O15" t="s" s="2">
         <v>164</v>
       </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>71</v>
       </c>
@@ -3447,19 +3533,19 @@
         <v>71</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>72</v>
@@ -3476,12 +3562,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>71</v>
       </c>
@@ -3490,7 +3578,7 @@
         <v>72</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
@@ -3499,7 +3587,7 @@
         <v>71</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>167</v>
@@ -3513,9 +3601,7 @@
       <c r="N16" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="O16" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>71</v>
       </c>
@@ -3563,7 +3649,7 @@
         <v>71</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>72</v>
@@ -3575,17 +3661,19 @@
         <v>90</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="B17" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>71</v>
       </c>
@@ -3597,7 +3685,7 @@
         <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>71</v>
@@ -3614,7 +3702,9 @@
       <c r="M17" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N17" s="2"/>
+      <c r="N17" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>71</v>
@@ -3663,19 +3753,19 @@
         <v>71</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -3683,21 +3773,23 @@
         <v>177</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>71</v>
@@ -3706,16 +3798,16 @@
         <v>71</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3753,19 +3845,19 @@
         <v>71</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>72</v>
@@ -3782,12 +3874,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>71</v>
       </c>
@@ -3799,29 +3893,27 @@
         <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>71</v>
       </c>
@@ -3845,13 +3937,13 @@
         <v>71</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>186</v>
+        <v>71</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>187</v>
+        <v>71</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>71</v>
@@ -3869,19 +3961,19 @@
         <v>71</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -3893,38 +3985,38 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>71</v>
@@ -3949,51 +4041,51 @@
         <v>71</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>195</v>
+        <v>71</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4004,10 +4096,10 @@
         <v>72</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>71</v>
@@ -4016,19 +4108,19 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>93</v>
+        <v>195</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>71</v>
@@ -4041,7 +4133,7 @@
         <v>71</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>204</v>
+        <v>71</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>71</v>
@@ -4077,13 +4169,13 @@
         <v>71</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>90</v>
@@ -4094,10 +4186,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4117,20 +4209,18 @@
         <v>71</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>71</v>
@@ -4143,7 +4233,7 @@
         <v>71</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>71</v>
@@ -4179,7 +4269,7 @@
         <v>71</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>72</v>
@@ -4188,29 +4278,29 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>71</v>
@@ -4219,19 +4309,19 @@
         <v>71</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>123</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>124</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4269,39 +4359,39 @@
         <v>71</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>218</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4318,24 +4408,26 @@
         <v>71</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>99</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>71</v>
       </c>
@@ -4359,13 +4451,13 @@
         <v>71</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>71</v>
@@ -4383,7 +4475,7 @@
         <v>71</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>72</v>
@@ -4395,15 +4487,15 @@
         <v>90</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>225</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4417,7 +4509,7 @@
         <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>71</v>
@@ -4426,26 +4518,24 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q25" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
         <v>71</v>
       </c>
@@ -4465,13 +4555,13 @@
         <v>71</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>71</v>
+        <v>223</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>71</v>
+        <v>224</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>71</v>
+        <v>225</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>71</v>
@@ -4506,10 +4596,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4523,7 +4613,7 @@
         <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>71</v>
@@ -4532,19 +4622,19 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>213</v>
+        <v>93</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>71</v>
@@ -4557,7 +4647,7 @@
         <v>71</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>71</v>
+        <v>232</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>71</v>
@@ -4605,15 +4695,15 @@
         <v>90</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>218</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4633,18 +4723,20 @@
         <v>71</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>71</v>
@@ -4657,7 +4749,7 @@
         <v>71</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>71</v>
+        <v>238</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>71</v>
@@ -4693,7 +4785,7 @@
         <v>71</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>72</v>
@@ -4702,29 +4794,29 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>71</v>
@@ -4733,19 +4825,19 @@
         <v>71</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>123</v>
+        <v>241</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>124</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>126</v>
+        <v>244</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4783,39 +4875,39 @@
         <v>71</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>131</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4838,16 +4930,16 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4897,7 +4989,7 @@
         <v>71</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>72</v>
@@ -4906,18 +4998,18 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>91</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4931,7 +5023,7 @@
         <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>71</v>
@@ -4940,23 +5032,25 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>71</v>
@@ -5001,7 +5095,7 @@
         <v>71</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>72</v>
@@ -5010,7 +5104,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>91</v>
@@ -5018,10 +5112,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5044,18 +5138,20 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>71</v>
       </c>
@@ -5103,7 +5199,7 @@
         <v>71</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>72</v>
@@ -5115,15 +5211,15 @@
         <v>90</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>225</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5137,26 +5233,24 @@
         <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>71</v>
@@ -5205,7 +5299,7 @@
         <v>71</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>72</v>
@@ -5214,22 +5308,22 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>225</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5245,23 +5339,21 @@
         <v>71</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>263</v>
+        <v>124</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>71</v>
       </c>
@@ -5285,31 +5377,31 @@
         <v>71</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>267</v>
+        <v>71</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>268</v>
+        <v>71</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>72</v>
@@ -5321,15 +5413,15 @@
         <v>90</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5349,18 +5441,20 @@
         <v>71</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>71</v>
@@ -5409,7 +5503,7 @@
         <v>71</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>176</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>72</v>
@@ -5418,29 +5512,29 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>71</v>
+        <v>273</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>71</v>
@@ -5449,25 +5543,27 @@
         <v>71</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>123</v>
+        <v>268</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>124</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>178</v>
+        <v>276</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>126</v>
+        <v>277</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q35" s="2"/>
+      <c r="Q35" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="R35" t="s" s="2">
         <v>71</v>
       </c>
@@ -5499,39 +5595,39 @@
         <v>71</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>90</v>
+        <v>273</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5542,10 +5638,10 @@
         <v>72</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>71</v>
@@ -5554,20 +5650,18 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>71</v>
       </c>
@@ -5603,41 +5697,41 @@
         <v>71</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AC36" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD36" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>91</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>71</v>
       </c>
@@ -5658,20 +5752,18 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>71</v>
       </c>
@@ -5695,13 +5787,13 @@
         <v>71</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>283</v>
+        <v>71</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>71</v>
@@ -5719,31 +5811,29 @@
         <v>71</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>91</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>71</v>
       </c>
@@ -5752,10 +5842,10 @@
         <v>72</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>71</v>
@@ -5764,19 +5854,19 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>272</v>
+        <v>218</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>71</v>
@@ -5801,31 +5891,31 @@
         <v>71</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>72</v>
@@ -5837,19 +5927,17 @@
         <v>90</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>71</v>
       </c>
@@ -5861,29 +5949,25 @@
         <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>272</v>
+        <v>201</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>293</v>
+        <v>202</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>71</v>
       </c>
@@ -5907,13 +5991,13 @@
         <v>71</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>71</v>
@@ -5931,65 +6015,61 @@
         <v>71</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>204</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>272</v>
+        <v>123</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>124</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>274</v>
+        <v>206</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>71</v>
       </c>
@@ -6013,31 +6093,31 @@
         <v>71</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>300</v>
+        <v>71</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>207</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>72</v>
@@ -6049,19 +6129,17 @@
         <v>90</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>71</v>
       </c>
@@ -6070,10 +6148,10 @@
         <v>72</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>71</v>
@@ -6082,19 +6160,19 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>71</v>
@@ -6119,31 +6197,29 @@
         <v>71</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB41" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>71</v>
-      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>72</v>
@@ -6160,13 +6236,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>71</v>
@@ -6188,19 +6264,19 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>71</v>
@@ -6225,13 +6301,13 @@
         <v>71</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>71</v>
@@ -6249,7 +6325,7 @@
         <v>71</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>72</v>
@@ -6266,13 +6342,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>71</v>
@@ -6294,19 +6370,19 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>71</v>
@@ -6331,13 +6407,13 @@
         <v>71</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>71</v>
@@ -6355,7 +6431,7 @@
         <v>71</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>72</v>
@@ -6372,13 +6448,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>71</v>
@@ -6400,19 +6476,19 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>71</v>
@@ -6437,13 +6513,13 @@
         <v>71</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>71</v>
@@ -6461,7 +6537,7 @@
         <v>71</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>72</v>
@@ -6481,7 +6557,7 @@
         <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>325</v>
@@ -6506,19 +6582,19 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>327</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>71</v>
@@ -6543,13 +6619,13 @@
         <v>71</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y45" t="s" s="2">
         <v>328</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>71</v>
@@ -6567,7 +6643,7 @@
         <v>71</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>72</v>
@@ -6584,13 +6660,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>71</v>
@@ -6612,19 +6688,19 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="O46" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>71</v>
@@ -6649,13 +6725,13 @@
         <v>71</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>71</v>
@@ -6673,7 +6749,7 @@
         <v>71</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>72</v>
@@ -6690,13 +6766,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>71</v>
@@ -6718,19 +6794,19 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>71</v>
@@ -6755,13 +6831,13 @@
         <v>71</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>71</v>
@@ -6779,7 +6855,7 @@
         <v>71</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>72</v>
@@ -6796,13 +6872,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>71</v>
@@ -6824,19 +6900,19 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>71</v>
@@ -6861,13 +6937,13 @@
         <v>71</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>71</v>
@@ -6885,7 +6961,7 @@
         <v>71</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>72</v>
@@ -6902,13 +6978,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>71</v>
@@ -6930,19 +7006,19 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>71</v>
@@ -6967,13 +7043,13 @@
         <v>71</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>71</v>
@@ -6991,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>72</v>
@@ -7008,13 +7084,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>71</v>
@@ -7036,19 +7112,19 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>71</v>
@@ -7073,13 +7149,13 @@
         <v>71</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>71</v>
@@ -7097,7 +7173,7 @@
         <v>71</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>72</v>
@@ -7114,13 +7190,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>71</v>
@@ -7142,19 +7218,19 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>71</v>
@@ -7179,13 +7255,13 @@
         <v>71</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>71</v>
@@ -7203,7 +7279,7 @@
         <v>71</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>72</v>
@@ -7220,12 +7296,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>71</v>
       </c>
@@ -7237,7 +7315,7 @@
         <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>71</v>
@@ -7246,19 +7324,19 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>173</v>
+        <v>300</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>302</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>364</v>
+        <v>304</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>71</v>
@@ -7283,13 +7361,13 @@
         <v>71</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>71</v>
+        <v>368</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>71</v>
+        <v>369</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>71</v>
@@ -7307,13 +7385,13 @@
         <v>71</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>365</v>
+        <v>306</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>90</v>
@@ -7324,12 +7402,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>71</v>
       </c>
@@ -7338,10 +7418,10 @@
         <v>72</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>71</v>
@@ -7350,18 +7430,20 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>71</v>
       </c>
@@ -7385,31 +7467,31 @@
         <v>71</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>373</v>
+        <v>71</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>374</v>
+        <v>71</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>72</v>
@@ -7426,13 +7508,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>71</v>
@@ -7442,7 +7524,7 @@
         <v>72</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -7454,18 +7536,20 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>71</v>
       </c>
@@ -7489,11 +7573,13 @@
         <v>71</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>71</v>
@@ -7511,7 +7597,7 @@
         <v>71</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>72</v>
@@ -7528,13 +7614,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>71</v>
@@ -7544,7 +7630,7 @@
         <v>72</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -7556,18 +7642,20 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>71</v>
       </c>
@@ -7591,13 +7679,13 @@
         <v>71</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>71</v>
@@ -7615,7 +7703,7 @@
         <v>71</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>72</v>
@@ -7632,13 +7720,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>71</v>
@@ -7648,7 +7736,7 @@
         <v>72</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -7660,18 +7748,20 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>71</v>
       </c>
@@ -7695,13 +7785,13 @@
         <v>71</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>71</v>
@@ -7719,7 +7809,7 @@
         <v>71</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>72</v>
@@ -7736,14 +7826,12 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>71</v>
       </c>
@@ -7752,10 +7840,10 @@
         <v>72</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>71</v>
@@ -7764,18 +7852,20 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>71</v>
       </c>
@@ -7799,13 +7889,13 @@
         <v>71</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>396</v>
+        <v>71</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>386</v>
+        <v>71</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>71</v>
@@ -7823,13 +7913,13 @@
         <v>71</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>90</v>
@@ -7840,14 +7930,12 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>71</v>
       </c>
@@ -7859,7 +7947,7 @@
         <v>73</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>71</v>
@@ -7868,16 +7956,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7903,31 +7991,31 @@
         <v>71</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="AC58" t="s" s="2">
-        <v>71</v>
+        <v>402</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>72</v>
@@ -7944,13 +8032,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>71</v>
@@ -7972,16 +8060,16 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8007,13 +8095,11 @@
         <v>71</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>71</v>
@@ -8031,7 +8117,7 @@
         <v>71</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>72</v>
@@ -8048,13 +8134,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>71</v>
@@ -8076,16 +8162,16 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8111,13 +8197,13 @@
         <v>71</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>71</v>
@@ -8135,7 +8221,7 @@
         <v>71</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>72</v>
@@ -8152,13 +8238,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>71</v>
@@ -8180,16 +8266,16 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8215,13 +8301,13 @@
         <v>71</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>71</v>
@@ -8239,7 +8325,7 @@
         <v>71</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>72</v>
@@ -8256,13 +8342,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>71</v>
@@ -8284,16 +8370,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8319,13 +8405,13 @@
         <v>71</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>71</v>
@@ -8343,7 +8429,7 @@
         <v>71</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>72</v>
@@ -8360,13 +8446,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>71</v>
@@ -8388,16 +8474,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8423,13 +8509,13 @@
         <v>71</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>71</v>
@@ -8447,7 +8533,7 @@
         <v>71</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>72</v>
@@ -8464,13 +8550,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>71</v>
@@ -8492,16 +8578,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8527,13 +8613,13 @@
         <v>71</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>71</v>
@@ -8551,7 +8637,7 @@
         <v>71</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>72</v>
@@ -8568,12 +8654,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>71</v>
       </c>
@@ -8594,16 +8682,16 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8629,13 +8717,13 @@
         <v>71</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>71</v>
+        <v>439</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>71</v>
+        <v>414</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>71</v>
@@ -8653,7 +8741,7 @@
         <v>71</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>433</v>
+        <v>394</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>72</v>
@@ -8665,17 +8753,19 @@
         <v>90</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>225</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>71</v>
       </c>
@@ -8693,19 +8783,19 @@
         <v>71</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>439</v>
+        <v>218</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>441</v>
+        <v>406</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8731,13 +8821,13 @@
         <v>71</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>71</v>
+        <v>444</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>71</v>
+        <v>414</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>71</v>
@@ -8755,7 +8845,7 @@
         <v>71</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>72</v>
@@ -8767,17 +8857,19 @@
         <v>90</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>225</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>71</v>
       </c>
@@ -8798,18 +8890,18 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>444</v>
+        <v>218</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>71</v>
       </c>
@@ -8833,29 +8925,31 @@
         <v>71</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>71</v>
+        <v>449</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>71</v>
+        <v>414</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AC67" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD67" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>443</v>
+        <v>394</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>72</v>
@@ -8867,7 +8961,7 @@
         <v>90</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>449</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -8875,7 +8969,7 @@
         <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>394</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>451</v>
@@ -8891,29 +8985,27 @@
         <v>73</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>447</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>71</v>
       </c>
@@ -8937,13 +9029,13 @@
         <v>71</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>71</v>
+        <v>454</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>71</v>
+        <v>414</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>71</v>
@@ -8961,7 +9053,7 @@
         <v>71</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>394</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>72</v>
@@ -8973,7 +9065,7 @@
         <v>90</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>449</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -8981,9 +9073,11 @@
         <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>71</v>
       </c>
@@ -9001,19 +9095,19 @@
         <v>71</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>456</v>
+        <v>218</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>457</v>
       </c>
       <c r="M69" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9039,13 +9133,13 @@
         <v>71</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>71</v>
+        <v>459</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>71</v>
+        <v>460</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>71</v>
@@ -9063,7 +9157,7 @@
         <v>71</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>455</v>
+        <v>394</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>72</v>
@@ -9080,10 +9174,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9094,27 +9188,29 @@
         <v>72</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>173</v>
+        <v>462</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>174</v>
+        <v>463</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>71</v>
@@ -9163,31 +9259,31 @@
         <v>71</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>176</v>
+        <v>461</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>71</v>
+        <v>253</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9197,7 +9293,7 @@
         <v>73</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>71</v>
@@ -9206,16 +9302,16 @@
         <v>71</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>123</v>
+        <v>467</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>124</v>
+        <v>468</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>178</v>
+        <v>469</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>126</v>
+        <v>470</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9253,19 +9349,19 @@
         <v>71</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>179</v>
+        <v>466</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>72</v>
@@ -9277,19 +9373,19 @@
         <v>90</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>131</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>463</v>
+        <v>71</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9299,28 +9395,26 @@
         <v>73</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>123</v>
+        <v>472</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>164</v>
+        <v>475</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>71</v>
@@ -9357,19 +9451,17 @@
         <v>71</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="AC72" s="2"/>
       <c r="AD72" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>72</v>
@@ -9381,17 +9473,19 @@
         <v>90</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>131</v>
+        <v>477</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>71</v>
       </c>
@@ -9412,18 +9506,20 @@
         <v>71</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>99</v>
+        <v>480</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>71</v>
       </c>
@@ -9447,31 +9543,31 @@
         <v>71</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>72</v>
@@ -9483,15 +9579,15 @@
         <v>90</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>91</v>
+        <v>477</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9502,10 +9598,10 @@
         <v>72</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>71</v>
@@ -9514,15 +9610,17 @@
         <v>71</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>227</v>
+        <v>484</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>71</v>
@@ -9571,13 +9669,13 @@
         <v>71</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>90</v>
@@ -9588,10 +9686,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9614,17 +9712,15 @@
         <v>71</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>477</v>
+        <v>201</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>478</v>
+        <v>202</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>71</v>
@@ -9673,7 +9769,7 @@
         <v>71</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>476</v>
+        <v>204</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>72</v>
@@ -9682,29 +9778,29 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>71</v>
@@ -9716,16 +9812,16 @@
         <v>71</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>477</v>
+        <v>123</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>482</v>
+        <v>124</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>483</v>
+        <v>206</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>480</v>
+        <v>126</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9763,43 +9859,43 @@
         <v>71</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>481</v>
+        <v>207</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>71</v>
+        <v>491</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -9809,25 +9905,29 @@
         <v>73</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I77" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I77" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="J77" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>71</v>
       </c>
@@ -9875,7 +9975,7 @@
         <v>71</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>72</v>
@@ -9887,15 +9987,15 @@
         <v>90</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9906,7 +10006,7 @@
         <v>72</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>71</v>
@@ -9918,15 +10018,17 @@
         <v>71</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>174</v>
+        <v>496</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>71</v>
@@ -9951,13 +10053,13 @@
         <v>71</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>71</v>
+        <v>499</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>71</v>
+        <v>500</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>71</v>
@@ -9975,38 +10077,38 @@
         <v>71</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>176</v>
+        <v>495</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>71</v>
@@ -10018,17 +10120,15 @@
         <v>71</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>123</v>
+        <v>255</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>124</v>
+        <v>502</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>71</v>
@@ -10065,75 +10165,73 @@
         <v>71</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>179</v>
+        <v>501</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>463</v>
+        <v>71</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>123</v>
+        <v>505</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>465</v>
+        <v>507</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>71</v>
       </c>
@@ -10181,27 +10279,27 @@
         <v>71</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>466</v>
+        <v>504</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10209,7 +10307,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>78</v>
@@ -10224,16 +10322,16 @@
         <v>71</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>173</v>
+        <v>505</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10283,10 +10381,10 @@
         <v>71</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>78</v>
@@ -10300,10 +10398,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10314,10 +10412,10 @@
         <v>72</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>71</v>
@@ -10326,17 +10424,15 @@
         <v>71</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>213</v>
+        <v>484</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>71</v>
@@ -10385,27 +10481,27 @@
         <v>71</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>218</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10419,7 +10515,7 @@
         <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>71</v>
@@ -10428,17 +10524,15 @@
         <v>71</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>497</v>
+        <v>202</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>71</v>
@@ -10487,7 +10581,7 @@
         <v>71</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>496</v>
+        <v>204</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>72</v>
@@ -10496,22 +10590,22 @@
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10521,7 +10615,7 @@
         <v>73</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>71</v>
@@ -10530,20 +10624,18 @@
         <v>71</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>500</v>
+        <v>123</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>501</v>
+        <v>124</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>502</v>
+        <v>206</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>71</v>
       </c>
@@ -10579,19 +10671,19 @@
         <v>71</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>499</v>
+        <v>207</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>72</v>
@@ -10603,11 +10695,525 @@
         <v>90</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ84">
+  <autoFilter ref="A1:AJ89">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10617,7 +11223,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
